--- a/lab4/out/lab4_recalculated.xlsx
+++ b/lab4/out/lab4_recalculated.xlsx
@@ -813,7 +813,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -839,7 +839,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -847,6 +847,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1291,11 +1295,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="98550537"/>
-        <c:axId val="37705824"/>
+        <c:axId val="79738338"/>
+        <c:axId val="41254946"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="98550537"/>
+        <c:axId val="79738338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1328,7 +1332,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37705824"/>
+        <c:crossAx val="41254946"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1336,7 +1340,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37705824"/>
+        <c:axId val="41254946"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1385,7 +1389,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1412,7 +1416,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98550537"/>
+        <c:crossAx val="79738338"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2413,7 +2417,7 @@
         <f aca="false">AVERAGE(C2:G2)</f>
         <v>4</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <f aca="false">RANK(H2,$H$2:$H$4)</f>
         <v>1</v>
       </c>
@@ -2444,7 +2448,7 @@
         <f aca="false">AVERAGE(C3:G3)</f>
         <v>3.8</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <f aca="false">RANK(H3,$H$2:$H$4)</f>
         <v>2</v>
       </c>
@@ -2475,7 +2479,7 @@
         <f aca="false">AVERAGE(C4:G4)</f>
         <v>2.2</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <f aca="false">RANK(H4,$H$2:$H$4)</f>
         <v>3</v>
       </c>
@@ -2528,13 +2532,13 @@
       <c r="B2" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="10" t="n">
         <v>150</v>
       </c>
     </row>
@@ -2545,13 +2549,13 @@
       <c r="B3" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="10" t="n">
         <v>110</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="10" t="n">
         <v>110</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="10" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2562,13 +2566,13 @@
       <c r="B4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2579,13 +2583,13 @@
       <c r="B5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2596,13 +2600,13 @@
       <c r="B6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2630,15 +2634,15 @@
       <c r="B8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <f aca="false">C7*x4_sup_rate</f>
         <v>3</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <f aca="false">D7*x4_sup_rate</f>
         <v>6</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <f aca="false">E7*x4_sup_rate</f>
         <v>15</v>
       </c>
@@ -2650,15 +2654,15 @@
       <c r="B9" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <f aca="false">C2+C3*C6</f>
         <v>135</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <f aca="false">D2+D3*D6</f>
         <v>270</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <f aca="false">E2+E3*E6</f>
         <v>600</v>
       </c>
@@ -2670,15 +2674,15 @@
       <c r="B10" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <f aca="false">C8+C6*x4_cogs</f>
         <v>19</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <f aca="false">D8+D6*x4_cogs</f>
         <v>38</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <f aca="false">E8+E6*x4_cogs</f>
         <v>95</v>
       </c>
@@ -2690,15 +2694,15 @@
       <c r="B11" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <f aca="false">C9-C10</f>
         <v>116</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <f aca="false">D9-D10</f>
         <v>232</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <f aca="false">E9-E10</f>
         <v>505</v>
       </c>
@@ -2710,15 +2714,15 @@
       <c r="B12" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <f aca="false">(C9-C10)/C9</f>
         <v>0.859259259259259</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <f aca="false">(D9-D10)/D9</f>
         <v>0.859259259259259</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <f aca="false">(E9-E10)/E9</f>
         <v>0.841666666666667</v>
       </c>
@@ -2730,15 +2734,15 @@
       <c r="B13" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <f aca="false">C10/(1-x4_gm)</f>
         <v>63.3333333333333</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <f aca="false">D10/(1-x4_gm)</f>
         <v>126.666666666667</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <f aca="false">E10/(1-x4_gm)</f>
         <v>316.666666666667</v>
       </c>
@@ -2750,15 +2754,15 @@
       <c r="B14" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="13" t="str">
+      <c r="C14" s="14" t="str">
         <f aca="false">IF(C9&gt;=C13,"так","ні")</f>
         <v>так</v>
       </c>
-      <c r="D14" s="13" t="str">
+      <c r="D14" s="14" t="str">
         <f aca="false">IF(D9&gt;=D13,"так","ні")</f>
         <v>так</v>
       </c>
-      <c r="E14" s="13" t="str">
+      <c r="E14" s="14" t="str">
         <f aca="false">IF(E9&gt;=E13,"так","ні")</f>
         <v>так</v>
       </c>
@@ -2770,15 +2774,15 @@
       <c r="B15" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="15" t="n">
         <f aca="false">(C9-C10)/C10</f>
         <v>6.10526315789474</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <f aca="false">(D9-D10)/D10</f>
         <v>6.10526315789474</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <f aca="false">(E9-E10)/E10</f>
         <v>5.31578947368421</v>
       </c>
@@ -2790,15 +2794,15 @@
       <c r="B16" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <f aca="false">C9/C6</f>
         <v>135</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <f aca="false">D9/D6</f>
         <v>135</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <f aca="false">E9/E6</f>
         <v>120</v>
       </c>
@@ -2810,15 +2814,15 @@
       <c r="B17" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="15" t="n">
         <f aca="false">C16/x4_value</f>
         <v>0.15</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="15" t="n">
         <f aca="false">D16/x4_value</f>
         <v>0.15</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="15" t="n">
         <f aca="false">E16/x4_value</f>
         <v>0.133333333333333</v>
       </c>
@@ -2830,15 +2834,15 @@
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C18" s="13" t="str">
+      <c r="C18" s="14" t="str">
         <f aca="false">IF(C3&gt;=x4_floor_unit,"так","ні")</f>
         <v>так</v>
       </c>
-      <c r="D18" s="13" t="str">
+      <c r="D18" s="14" t="str">
         <f aca="false">IF(D3&gt;=x4_floor_unit,"так","ні")</f>
         <v>так</v>
       </c>
-      <c r="E18" s="13" t="str">
+      <c r="E18" s="14" t="str">
         <f aca="false">IF(E3&gt;=x4_floor_unit,"так","ні")</f>
         <v>так</v>
       </c>
@@ -2850,15 +2854,15 @@
       <c r="B19" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="15" t="n">
         <f aca="false">C8/C10</f>
         <v>0.157894736842105</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="15" t="n">
         <f aca="false">D8/D10</f>
         <v>0.157894736842105</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <f aca="false">E8/E10</f>
         <v>0.157894736842105</v>
       </c>
@@ -2882,7 +2886,7 @@
         <f aca="false">x4_cogs_var/(1-x4_gm)</f>
         <v>53.3333333333333</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="15" t="n">
         <f aca="false">(B22-x4_cogs_var)/B22</f>
         <v>0.7</v>
       </c>
@@ -2895,7 +2899,7 @@
         <f aca="false">x4_cogs_var*(1+x4_gm)</f>
         <v>27.2</v>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="15" t="n">
         <f aca="false">(B23-x4_cogs_var)/B23</f>
         <v>0.411764705882353</v>
       </c>
@@ -2948,13 +2952,13 @@
       <c r="B2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="11" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2965,15 +2969,15 @@
       <c r="B3" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="14" t="n">
         <f aca="false">Тарифи!C2+Тарифи!C3*C2</f>
         <v>245</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="14" t="n">
         <f aca="false">Тарифи!D2+Тарифи!D3*D2</f>
         <v>600</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="14" t="n">
         <f aca="false">Тарифи!E2+Тарифи!E3*E2</f>
         <v>1950</v>
       </c>
@@ -2985,15 +2989,15 @@
       <c r="B4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="14" t="n">
         <f aca="false">Тарифи!C8+C2*x4_cogs_high</f>
         <v>64.76</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="14" t="n">
         <f aca="false">Тарифи!D8+D2*x4_cogs_high</f>
         <v>160.4</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="14" t="n">
         <f aca="false">Тарифи!E8+E2*x4_cogs_high</f>
         <v>632.6</v>
       </c>
@@ -3003,15 +3007,15 @@
         <v>173</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="15" t="n">
         <f aca="false">(C3-C4)/C3</f>
         <v>0.735673469387755</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <f aca="false">(D3-D4)/D3</f>
         <v>0.732666666666667</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <f aca="false">(E3-E4)/E3</f>
         <v>0.675589743589744</v>
       </c>
@@ -3023,15 +3027,15 @@
       <c r="B6" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">C2*x4_over</f>
         <v>110</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <f aca="false">D2*x4_over</f>
         <v>275</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <f aca="false">E2*x4_over</f>
         <v>1100</v>
       </c>
@@ -3041,15 +3045,15 @@
         <v>176</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">C3+C6</f>
         <v>355</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <f aca="false">D3+D6</f>
         <v>875</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <f aca="false">E3+E6</f>
         <v>3050</v>
       </c>
@@ -3059,15 +3063,15 @@
         <v>177</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <f aca="false">(C7-C4)/C7</f>
         <v>0.817577464788732</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <f aca="false">(D7-D4)/D7</f>
         <v>0.816685714285714</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <f aca="false">(E7-E4)/E7</f>
         <v>0.792590163934426</v>
       </c>
@@ -3077,15 +3081,15 @@
         <v>178</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="13" t="str">
+      <c r="C9" s="14" t="str">
         <f aca="false">IF(C5&gt;=x4_gm,"так","ні")</f>
         <v>так</v>
       </c>
-      <c r="D9" s="13" t="str">
+      <c r="D9" s="14" t="str">
         <f aca="false">IF(D5&gt;=x4_gm,"так","ні")</f>
         <v>так</v>
       </c>
-      <c r="E9" s="13" t="str">
+      <c r="E9" s="14" t="str">
         <f aca="false">IF(E5&gt;=x4_gm,"так","ні")</f>
         <v>ні</v>
       </c>
@@ -3095,15 +3099,15 @@
         <v>179</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="13" t="str">
+      <c r="C10" s="14" t="str">
         <f aca="false">IF(C8&gt;=x4_gm,"так","ні")</f>
         <v>так</v>
       </c>
-      <c r="D10" s="13" t="str">
+      <c r="D10" s="14" t="str">
         <f aca="false">IF(D8&gt;=x4_gm,"так","ні")</f>
         <v>так</v>
       </c>
-      <c r="E10" s="13" t="str">
+      <c r="E10" s="14" t="str">
         <f aca="false">IF(E8&gt;=x4_gm,"так","ні")</f>
         <v>так</v>
       </c>
@@ -3149,13 +3153,13 @@
       <c r="A2" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B2" s="16" t="n">
         <v>0.7</v>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="16" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -3163,15 +3167,15 @@
       <c r="A3" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <f aca="false">x4_scale*B2</f>
         <v>59.5</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <f aca="false">x4_scale*C2</f>
         <v>85</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <f aca="false">x4_scale*D2</f>
         <v>119</v>
       </c>
@@ -3180,15 +3184,15 @@
       <c r="A4" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <f aca="false">x4_mix_B*x4_use_B+x4_mix_S*x4_use_S+x4_mix_P*x4_use_P</f>
         <v>1.7</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <f aca="false">x4_mix_B*x4_use_B+x4_mix_S*x4_use_S+x4_mix_P*x4_use_P</f>
         <v>1.7</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <f aca="false">x4_mix_B*x4_use_B+x4_mix_S*x4_use_S+x4_mix_P*x4_use_P</f>
         <v>1.7</v>
       </c>
@@ -3197,15 +3201,15 @@
       <c r="A5" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <f aca="false">B3/B4</f>
         <v>35</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <f aca="false">C3/C4</f>
         <v>50</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <f aca="false">D3/D4</f>
         <v>70</v>
       </c>
@@ -3214,15 +3218,15 @@
       <c r="A6" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <f aca="false">B5*x4_mix_B</f>
         <v>21</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <f aca="false">C5*x4_mix_B</f>
         <v>30</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <f aca="false">D5*x4_mix_B</f>
         <v>42</v>
       </c>
@@ -3231,15 +3235,15 @@
       <c r="A7" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <f aca="false">B5*x4_mix_S</f>
         <v>10.5</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <f aca="false">C5*x4_mix_S</f>
         <v>15</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">D5*x4_mix_S</f>
         <v>21</v>
       </c>
@@ -3248,15 +3252,15 @@
       <c r="A8" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <f aca="false">B5*x4_mix_P</f>
         <v>3.5</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <f aca="false">C5*x4_mix_P</f>
         <v>5</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">D5*x4_mix_P</f>
         <v>7</v>
       </c>
@@ -3265,15 +3269,15 @@
       <c r="A9" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <f aca="false">B6*x4_base_B+B7*x4_base_S+B8*x4_base_P</f>
         <v>1575</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <f aca="false">C6*x4_base_B+C7*x4_base_S+C8*x4_base_P</f>
         <v>2250</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <f aca="false">D6*x4_base_B+D7*x4_base_S+D8*x4_base_P</f>
         <v>3150</v>
       </c>
@@ -3282,15 +3286,15 @@
       <c r="A10" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <f aca="false">B6*x4_use_B*x4_pb_B+B7*x4_use_S*x4_pb_S+B8*x4_use_P*x4_pb_P</f>
         <v>6195</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <f aca="false">C6*x4_use_B*x4_pb_B+C7*x4_use_S*x4_pb_S+C8*x4_use_P*x4_pb_P</f>
         <v>8850</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <f aca="false">D6*x4_use_B*x4_pb_B+D7*x4_use_S*x4_pb_S+D8*x4_use_P*x4_pb_P</f>
         <v>12390</v>
       </c>
@@ -3299,15 +3303,15 @@
       <c r="A11" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <f aca="false">B3*x4_high_share</f>
         <v>5.95</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <f aca="false">C3*x4_high_share</f>
         <v>8.5</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">D3*x4_high_share</f>
         <v>11.9</v>
       </c>
@@ -3316,15 +3320,15 @@
       <c r="A12" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <f aca="false">B11*x4_over</f>
         <v>327.25</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <f aca="false">C11*x4_over</f>
         <v>467.5</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <f aca="false">D11*x4_over</f>
         <v>654.5</v>
       </c>
@@ -3333,15 +3337,15 @@
       <c r="A13" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <f aca="false">B9+B10+B12</f>
         <v>8097.25</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <f aca="false">C9+C10+C12</f>
         <v>11567.5</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <f aca="false">D9+D10+D12</f>
         <v>16194.5</v>
       </c>
@@ -3350,15 +3354,15 @@
       <c r="A14" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <f aca="false">B6*x4_cc_B+B7*x4_cc_S+B8*x4_cc_P</f>
         <v>178.5</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <f aca="false">C6*x4_cc_B+C7*x4_cc_S+C8*x4_cc_P</f>
         <v>255</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <f aca="false">D6*x4_cc_B+D7*x4_cc_S+D8*x4_cc_P</f>
         <v>357</v>
       </c>
@@ -3367,15 +3371,15 @@
       <c r="A15" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <f aca="false">(B3-B11)*x4_cogs+B11*x4_cogs_high</f>
         <v>1040.536</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <f aca="false">(C3-C11)*x4_cogs+C11*x4_cogs_high</f>
         <v>1486.48</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <f aca="false">(D3-D11)*x4_cogs+D11*x4_cogs_high</f>
         <v>2081.072</v>
       </c>
@@ -3384,15 +3388,15 @@
       <c r="A16" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <f aca="false">B14+B15</f>
         <v>1219.036</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <f aca="false">C14+C15</f>
         <v>1741.48</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <f aca="false">D14+D15</f>
         <v>2438.072</v>
       </c>
@@ -3401,15 +3405,15 @@
       <c r="A17" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <f aca="false">B13-B16</f>
         <v>6878.214</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <f aca="false">C13-C16</f>
         <v>9826.02</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <f aca="false">D13-D16</f>
         <v>13756.428</v>
       </c>
@@ -3418,15 +3422,15 @@
       <c r="A18" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="15" t="n">
         <f aca="false">B17/B13</f>
         <v>0.84945061594986</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="15" t="n">
         <f aca="false">C17/C13</f>
         <v>0.84945061594986</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <f aca="false">D17/D13</f>
         <v>0.84945061594986</v>
       </c>
@@ -3435,15 +3439,15 @@
       <c r="A19" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="14" t="n">
         <f aca="false">B13/B5</f>
         <v>231.35</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <f aca="false">C13/C5</f>
         <v>231.35</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <f aca="false">D13/D5</f>
         <v>231.35</v>
       </c>
@@ -3452,15 +3456,15 @@
       <c r="A20" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
         <f aca="false">B13/B3</f>
         <v>136.088235294118</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <f aca="false">C13/C3</f>
         <v>136.088235294118</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <f aca="false">D13/D3</f>
         <v>136.088235294118</v>
       </c>

--- a/lab4/out/lab4_recalculated.xlsx
+++ b/lab4/out/lab4_recalculated.xlsx
@@ -22,19 +22,20 @@
     <definedName function="false" hidden="false" name="x4_cc_B" vbProcedure="false">Тарифи!$C$8</definedName>
     <definedName function="false" hidden="false" name="x4_cc_P" vbProcedure="false">Тарифи!$E$8</definedName>
     <definedName function="false" hidden="false" name="x4_cc_S" vbProcedure="false">Тарифи!$D$8</definedName>
-    <definedName function="false" hidden="false" name="x4_cogs" vbProcedure="false">'Параметри ЛР4'!$C$21</definedName>
-    <definedName function="false" hidden="false" name="x4_cogs_high" vbProcedure="false">'Параметри ЛР4'!$C$22</definedName>
+    <definedName function="false" hidden="false" name="x4_cogs" vbProcedure="false">'Параметри ЛР4'!$C$22</definedName>
+    <definedName function="false" hidden="false" name="x4_cogs_high" vbProcedure="false">'Параметри ЛР4'!$C$23</definedName>
     <definedName function="false" hidden="false" name="x4_cogs_var" vbProcedure="false">'Параметри ЛР4'!$C$2</definedName>
     <definedName function="false" hidden="false" name="x4_energy" vbProcedure="false">'Параметри ЛР4'!$C$18</definedName>
+    <definedName function="false" hidden="false" name="x4_episode" vbProcedure="false">'Параметри ЛР4'!$C$20</definedName>
     <definedName function="false" hidden="false" name="x4_fee" vbProcedure="false">'Параметри ЛР4'!$C$15</definedName>
-    <definedName function="false" hidden="false" name="x4_floor_unit" vbProcedure="false">'Параметри ЛР4'!$C$24</definedName>
+    <definedName function="false" hidden="false" name="x4_floor_unit" vbProcedure="false">'Параметри ЛР4'!$C$25</definedName>
     <definedName function="false" hidden="false" name="x4_gain" vbProcedure="false">'Параметри ЛР4'!$C$19</definedName>
     <definedName function="false" hidden="false" name="x4_gm" vbProcedure="false">'Параметри ЛР4'!$C$3</definedName>
     <definedName function="false" hidden="false" name="x4_high_share" vbProcedure="false">'Параметри ЛР4'!$C$16</definedName>
     <definedName function="false" hidden="false" name="x4_mix_B" vbProcedure="false">Тарифи!$C$5</definedName>
     <definedName function="false" hidden="false" name="x4_mix_P" vbProcedure="false">Тарифи!$E$5</definedName>
     <definedName function="false" hidden="false" name="x4_mix_S" vbProcedure="false">Тарифи!$D$5</definedName>
-    <definedName function="false" hidden="false" name="x4_over" vbProcedure="false">'Параметри ЛР4'!$C$23</definedName>
+    <definedName function="false" hidden="false" name="x4_over" vbProcedure="false">'Параметри ЛР4'!$C$24</definedName>
     <definedName function="false" hidden="false" name="x4_pb_B" vbProcedure="false">Тарифи!$C$3</definedName>
     <definedName function="false" hidden="false" name="x4_pb_P" vbProcedure="false">Тарифи!$E$3</definedName>
     <definedName function="false" hidden="false" name="x4_pb_S" vbProcedure="false">Тарифи!$D$3</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="237">
   <si>
     <t xml:space="preserve">Ім'я</t>
   </si>
@@ -252,6 +253,18 @@
     <t xml:space="preserve">альтернатива 2</t>
   </si>
   <si>
+    <t xml:space="preserve">x4_episode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тривалість епізоду нестабільності</t>
+  </si>
+  <si>
+    <t xml:space="preserve">міс.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A9</t>
+  </si>
+  <si>
     <t xml:space="preserve">x4_cogs</t>
   </si>
   <si>
@@ -399,6 +412,33 @@
     <t xml:space="preserve">Revenue, COGS</t>
   </si>
   <si>
+    <t xml:space="preserve">A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Готовність платити за будівлю</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130...135 EUR на місяць за будівлю, не більше 15% цінності 900 EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">П: гіпотеза A2 ЛР № 1, листами про намір не перевірена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue, GM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стаціонарний стан доплати за нестабільний облік</t>
+  </si>
+  <si>
+    <t xml:space="preserve">у сценаріях Y3 усі будівлі зі статусом «нестабільний облік» уже пройшли 2 місяці спостереження і 1 пільговий місяць; епізод нестабільності триває 12 місяців</t>
+  </si>
+  <si>
+    <t xml:space="preserve">П: спрощення; вплив від 1 до 3 неоплачених місяців наведено в додатку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue overage, GM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Модель</t>
   </si>
   <si>
@@ -549,6 +589,33 @@
     <t xml:space="preserve">COGS бази / COGS клієнта</t>
   </si>
   <si>
+    <t xml:space="preserve">Очікуваний COGS будівлі з A3, EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,9 × 16 + 0,1 × 30,88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Очікуваний COGS клієнта з A3, EUR/міс.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COGS бази + usage × 17,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Очікуваний overage з A3, EUR/міс.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">usage × 0,10 × 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Очікуваний рахунок з A3, EUR/міс.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">рахунок + overage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin з A3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Перевірка формули floor</t>
   </si>
   <si>
@@ -564,6 +631,15 @@
     <t xml:space="preserve">Помилково: COGS × (1 + GM)</t>
   </si>
   <si>
+    <t xml:space="preserve">Зважена за A1 gross margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Типова будівля, без A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">З урахуванням A3, дорівнює GM сценаріїв</t>
+  </si>
+  <si>
     <t xml:space="preserve">Формула</t>
   </si>
   <si>
@@ -604,6 +680,36 @@
   </si>
   <si>
     <t xml:space="preserve">Межа 70% виконана з правилом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неоплачених місяців з 12 (A9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overage, базовий сценарій, EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overage − буд. high × 50 × m / 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue, базовий сценарій, EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue − та сама втрата</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin, базовий сценарій</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM Pro, 20 буд., неоплачений місяць</t>
+  </si>
+  <si>
+    <t xml:space="preserve">рахунок без доплати</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM Pro, 20 буд., за 12 місяців</t>
+  </si>
+  <si>
+    <t xml:space="preserve">зважено за місяцями</t>
   </si>
   <si>
     <t xml:space="preserve">Показник за місяць, EUR</t>
@@ -676,7 +782,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
@@ -684,8 +790,9 @@
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
     <numFmt numFmtId="169" formatCode="0"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="0.00%"/>
+    <numFmt numFmtId="172" formatCode="0%"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -813,7 +920,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -878,11 +985,19 @@
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1295,11 +1410,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="79738338"/>
-        <c:axId val="41254946"/>
+        <c:axId val="9209015"/>
+        <c:axId val="6385966"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="79738338"/>
+        <c:axId val="9209015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1332,7 +1447,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41254946"/>
+        <c:crossAx val="6385966"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1340,7 +1455,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41254946"/>
+        <c:axId val="6385966"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1416,7 +1531,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79738338"/>
+        <c:crossAx val="9209015"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1686,7 +1801,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -2078,96 +2193,116 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="5" t="n">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="5" t="n">
         <f aca="false">x4_readings+x4_sim+x4_sms_cost*x4_sms_typ+x4_sup_h*x4_sup_rate</f>
         <v>16</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="6" t="str">
-        <f aca="false">IF(ABS(C21-x4_cogs_var)&lt;0.001,"збігається з варіантом","розбіжність")</f>
+      <c r="E22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="6" t="str">
+        <f aca="false">IF(ABS(C22-x4_cogs_var)&lt;0.001,"збігається з варіантом","розбіжність")</f>
         <v>збігається з варіантом</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="5" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="5" t="n">
         <f aca="false">x4_cogs+(x4_sms_high-x4_sms_typ)*x4_sms_cost+(x4_sup_high-x4_sup_h)*x4_sup_rate</f>
         <v>30.88</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="E23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="5" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="5" t="n">
         <f aca="false">x4_fee+MAX(x4_sms_high-x4_sms_incl,0)*x4_sms_price</f>
         <v>55</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="5" t="n">
+      <c r="E24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="5" t="n">
         <f aca="false">x4_cogs_var/(1-x4_gm)</f>
         <v>53.3333333333333</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>72</v>
+      <c r="E25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2186,7 +2321,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2198,53 +2333,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2252,84 +2387,118 @@
         <v>46</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2364,39 +2533,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>4</v>
@@ -2424,10 +2593,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>5</v>
@@ -2455,10 +2624,10 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1</v>
@@ -2500,7 +2669,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -2513,24 +2682,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C2" s="10" t="n">
         <v>25</v>
@@ -2544,10 +2713,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C3" s="10" t="n">
         <v>110</v>
@@ -2561,7 +2730,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>52</v>
@@ -2578,10 +2747,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>0.6</v>
@@ -2595,10 +2764,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1</v>
@@ -2612,10 +2781,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.1</v>
@@ -2629,10 +2798,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">C7*x4_sup_rate</f>
@@ -2649,10 +2818,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">C2+C3*C6</f>
@@ -2669,10 +2838,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">C8+C6*x4_cogs</f>
@@ -2689,10 +2858,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">C9-C10</f>
@@ -2709,10 +2878,10 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">(C9-C10)/C9</f>
@@ -2729,10 +2898,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C13" s="14" t="n">
         <f aca="false">C10/(1-x4_gm)</f>
@@ -2749,10 +2918,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C14" s="14" t="str">
         <f aca="false">IF(C9&gt;=C13,"так","ні")</f>
@@ -2769,10 +2938,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C15" s="15" t="n">
         <f aca="false">(C9-C10)/C10</f>
@@ -2789,10 +2958,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">C9/C6</f>
@@ -2809,10 +2978,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">C16/x4_value</f>
@@ -2829,10 +2998,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C18" s="14" t="str">
         <f aca="false">IF(C3&gt;=x4_floor_unit,"так","ні")</f>
@@ -2849,10 +3018,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">C8/C10</f>
@@ -2867,41 +3036,167 @@
         <v>0.157894736842105</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <f aca="false">(1-x4_high_share)*x4_cogs+x4_high_share*x4_cogs_high</f>
+        <v>17.488</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <f aca="false">(1-x4_high_share)*x4_cogs+x4_high_share*x4_cogs_high</f>
+        <v>17.488</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <f aca="false">(1-x4_high_share)*x4_cogs+x4_high_share*x4_cogs_high</f>
+        <v>17.488</v>
+      </c>
+    </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>163</v>
+      <c r="A21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <f aca="false">C8+C6*C20</f>
+        <v>20.488</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <f aca="false">D8+D6*D20</f>
+        <v>40.976</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <f aca="false">E8+E6*E20</f>
+        <v>102.44</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B22" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <f aca="false">C6*x4_high_share*x4_over</f>
+        <v>5.5</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <f aca="false">D6*x4_high_share*x4_over</f>
+        <v>11</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <f aca="false">E6*x4_high_share*x4_over</f>
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <f aca="false">C9+C22</f>
+        <v>140.5</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <f aca="false">D9+D22</f>
+        <v>281</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <f aca="false">E9+E22</f>
+        <v>627.5</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <f aca="false">(C23-C21)/C23</f>
+        <v>0.854177935943061</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <f aca="false">(D23-D21)/D23</f>
+        <v>0.854177935943061</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <f aca="false">(E23-E21)/E23</f>
+        <v>0.836749003984064</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B27" s="5" t="n">
         <f aca="false">x4_cogs_var/(1-x4_gm)</f>
         <v>53.3333333333333</v>
       </c>
-      <c r="C22" s="15" t="n">
-        <f aca="false">(B22-x4_cogs_var)/B22</f>
+      <c r="C27" s="15" t="n">
+        <f aca="false">(B27-x4_cogs_var)/B27</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B23" s="5" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="5" t="n">
         <f aca="false">x4_cogs_var*(1+x4_gm)</f>
         <v>27.2</v>
       </c>
-      <c r="C23" s="15" t="n">
-        <f aca="false">(B23-x4_cogs_var)/B23</f>
+      <c r="C28" s="15" t="n">
+        <f aca="false">(B28-x4_cogs_var)/B28</f>
         <v>0.411764705882353</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="16" t="n">
+        <f aca="false">(x4_mix_B*(C9-C10)+x4_mix_S*(D9-D10)+x4_mix_P*(E9-E10))/(x4_mix_B*C9+x4_mix_S*D9+x4_mix_P*E9)</f>
+        <v>0.854504504504504</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" s="16" t="n">
+        <f aca="false">(x4_mix_B*(C23-C21)+x4_mix_S*(D23-D21)+x4_mix_P*(E23-E21))/(x4_mix_B*C23+x4_mix_S*D23+x4_mix_P*E23)</f>
+        <v>0.84945061594986</v>
       </c>
     </row>
   </sheetData>
@@ -2920,12 +3215,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2933,24 +3228,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>2</v>
@@ -2964,10 +3259,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C3" s="14" t="n">
         <f aca="false">Тарифи!C2+Тарифи!C3*C2</f>
@@ -2984,10 +3279,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C4" s="14" t="n">
         <f aca="false">Тарифи!C8+C2*x4_cogs_high</f>
@@ -3004,7 +3299,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15" t="n">
@@ -3022,10 +3317,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C6" s="14" t="n">
         <f aca="false">C2*x4_over</f>
@@ -3042,7 +3337,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="14" t="n">
@@ -3060,7 +3355,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="15" t="n">
@@ -3078,7 +3373,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="14" t="str">
@@ -3096,7 +3391,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="14" t="str">
@@ -3110,6 +3405,146 @@
       <c r="E10" s="14" t="str">
         <f aca="false">IF(E8&gt;=x4_gm,"так","ні")</f>
         <v>так</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <f aca="false">Сценарії!$C$12-Сценарії!$C$11*x4_fee*C12/x4_episode</f>
+        <v>467.5</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">Сценарії!$C$12-Сценарії!$C$11*x4_fee*D12/x4_episode</f>
+        <v>432.083333333333</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <f aca="false">Сценарії!$C$12-Сценарії!$C$11*x4_fee*E12/x4_episode</f>
+        <v>396.666666666667</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <f aca="false">Сценарії!$C$12-Сценарії!$C$11*x4_fee*F12/x4_episode</f>
+        <v>361.25</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <f aca="false">Сценарії!$C$13-Сценарії!$C$11*x4_fee*C12/x4_episode</f>
+        <v>11567.5</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">Сценарії!$C$13-Сценарії!$C$11*x4_fee*D12/x4_episode</f>
+        <v>11532.0833333333</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <f aca="false">Сценарії!$C$13-Сценарії!$C$11*x4_fee*E12/x4_episode</f>
+        <v>11496.6666666667</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <f aca="false">Сценарії!$C$13-Сценарії!$C$11*x4_fee*F12/x4_episode</f>
+        <v>11461.25</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <f aca="false">(C14-Сценарії!$C$16)/C14</f>
+        <v>0.84945061594986</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <f aca="false">(D14-Сценарії!$C$16)/D14</f>
+        <v>0.84898825739784</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <f aca="false">(E14-Сценарії!$C$16)/E14</f>
+        <v>0.848523050159467</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <f aca="false">(F14-Сценарії!$C$16)/F14</f>
+        <v>0.848054967826372</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <f aca="false">($E$7-$E$2*x4_fee-$E$4)/($E$7-$E$2*x4_fee)</f>
+        <v>0.691414634146342</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <f aca="false">($E$7-$E$2*x4_fee-$E$4)/($E$7-$E$2*x4_fee)</f>
+        <v>0.691414634146342</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <f aca="false">($E$7-$E$2*x4_fee-$E$4)/($E$7-$E$2*x4_fee)</f>
+        <v>0.691414634146342</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <f aca="false">($E$7-$E$2*x4_fee-$E$4)/($E$7-$E$2*x4_fee)</f>
+        <v>0.691414634146342</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <f aca="false">($E$7*(x4_episode-C12)+($E$7-$E$2*x4_fee)*C12-x4_episode*$E$4)/($E$7*(x4_episode-C12)+($E$7-$E$2*x4_fee)*C12)</f>
+        <v>0.792590163934426</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <f aca="false">($E$7*(x4_episode-D12)+($E$7-$E$2*x4_fee)*D12-x4_episode*$E$4)/($E$7*(x4_episode-D12)+($E$7-$E$2*x4_fee)*D12)</f>
+        <v>0.78676404494382</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <f aca="false">($E$7*(x4_episode-E12)+($E$7-$E$2*x4_fee)*E12-x4_episode*$E$4)/($E$7*(x4_episode-E12)+($E$7-$E$2*x4_fee)*E12)</f>
+        <v>0.780601156069364</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <f aca="false">($E$7*(x4_episode-F12)+($E$7-$E$2*x4_fee)*F12-x4_episode*$E$4)/($E$7*(x4_episode-F12)+($E$7-$E$2*x4_fee)*F12)</f>
+        <v>0.774071428571429</v>
       </c>
     </row>
   </sheetData>
@@ -3137,137 +3572,137 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B2" s="16" t="n">
+        <v>219</v>
+      </c>
+      <c r="B2" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="18" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="17" t="n">
+        <v>220</v>
+      </c>
+      <c r="B3" s="19" t="n">
         <f aca="false">x4_scale*B2</f>
         <v>59.5</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="19" t="n">
         <f aca="false">x4_scale*C2</f>
         <v>85</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="19" t="n">
         <f aca="false">x4_scale*D2</f>
         <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B4" s="17" t="n">
+        <v>221</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <f aca="false">x4_mix_B*x4_use_B+x4_mix_S*x4_use_S+x4_mix_P*x4_use_P</f>
         <v>1.7</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <f aca="false">x4_mix_B*x4_use_B+x4_mix_S*x4_use_S+x4_mix_P*x4_use_P</f>
         <v>1.7</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="19" t="n">
         <f aca="false">x4_mix_B*x4_use_B+x4_mix_S*x4_use_S+x4_mix_P*x4_use_P</f>
         <v>1.7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="17" t="n">
+        <v>222</v>
+      </c>
+      <c r="B5" s="19" t="n">
         <f aca="false">B3/B4</f>
         <v>35</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="19" t="n">
         <f aca="false">C3/C4</f>
         <v>50</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="19" t="n">
         <f aca="false">D3/D4</f>
         <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="17" t="n">
+        <v>223</v>
+      </c>
+      <c r="B6" s="19" t="n">
         <f aca="false">B5*x4_mix_B</f>
         <v>21</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="19" t="n">
         <f aca="false">C5*x4_mix_B</f>
         <v>30</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="19" t="n">
         <f aca="false">D5*x4_mix_B</f>
         <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="17" t="n">
+        <v>224</v>
+      </c>
+      <c r="B7" s="19" t="n">
         <f aca="false">B5*x4_mix_S</f>
         <v>10.5</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="19" t="n">
         <f aca="false">C5*x4_mix_S</f>
         <v>15</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="19" t="n">
         <f aca="false">D5*x4_mix_S</f>
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="17" t="n">
+        <v>225</v>
+      </c>
+      <c r="B8" s="19" t="n">
         <f aca="false">B5*x4_mix_P</f>
         <v>3.5</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="19" t="n">
         <f aca="false">C5*x4_mix_P</f>
         <v>5</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="19" t="n">
         <f aca="false">D5*x4_mix_P</f>
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">B6*x4_base_B+B7*x4_base_S+B8*x4_base_P</f>
@@ -3284,7 +3719,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">B6*x4_use_B*x4_pb_B+B7*x4_use_S*x4_pb_S+B8*x4_use_P*x4_pb_P</f>
@@ -3301,24 +3736,24 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B11" s="17" t="n">
+        <v>228</v>
+      </c>
+      <c r="B11" s="19" t="n">
         <f aca="false">B3*x4_high_share</f>
         <v>5.95</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="19" t="n">
         <f aca="false">C3*x4_high_share</f>
         <v>8.5</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="19" t="n">
         <f aca="false">D3*x4_high_share</f>
         <v>11.9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="B12" s="14" t="n">
         <f aca="false">B11*x4_over</f>
@@ -3335,7 +3770,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">B9+B10+B12</f>
@@ -3352,7 +3787,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">B6*x4_cc_B+B7*x4_cc_S+B8*x4_cc_P</f>
@@ -3369,7 +3804,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="B15" s="14" t="n">
         <f aca="false">(B3-B11)*x4_cogs+B11*x4_cogs_high</f>
@@ -3386,7 +3821,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="B16" s="14" t="n">
         <f aca="false">B14+B15</f>
@@ -3403,7 +3838,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">B13-B16</f>
@@ -3420,7 +3855,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B18" s="15" t="n">
         <f aca="false">B17/B13</f>
@@ -3437,7 +3872,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="B19" s="14" t="n">
         <f aca="false">B13/B5</f>
@@ -3454,7 +3889,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">B13/B3</f>

--- a/lab4/out/lab4_recalculated.xlsx
+++ b/lab4/out/lab4_recalculated.xlsx
@@ -418,10 +418,10 @@
     <t xml:space="preserve">Готовність платити за будівлю</t>
   </si>
   <si>
-    <t xml:space="preserve">130...135 EUR на місяць за будівлю, не більше 15% цінності 900 EUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">П: гіпотеза A2 ЛР № 1, листами про намір не перевірена</t>
+    <t xml:space="preserve">130...135 EUR на місяць за будівлю, не більше 15% цінності 900 EUR; тест: не менше 3 листів про намір з 10 інтерв'ю за ціною 135 EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">П: гіпотеза A2 ЛР № 1, листами про намір не перевірена; поріг тесту A2 ЛР № 1 переглянуто з 130 до 135 EUR, бо рахунок Basic за 1 будівлю дорівнює 135 EUR</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue, GM</t>
@@ -1410,11 +1410,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="9209015"/>
-        <c:axId val="6385966"/>
+        <c:axId val="28489409"/>
+        <c:axId val="94276532"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9209015"/>
+        <c:axId val="28489409"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1447,7 +1447,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6385966"/>
+        <c:crossAx val="94276532"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1455,7 +1455,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6385966"/>
+        <c:axId val="94276532"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1531,7 +1531,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9209015"/>
+        <c:crossAx val="28489409"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2467,7 +2467,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>115</v>
       </c>
